--- a/public/templates/journals_printed_template.xlsx
+++ b/public/templates/journals_printed_template.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G3"/>
+  <dimension ref="A1:H3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -452,6 +452,11 @@
           <t>Publisher</t>
         </is>
       </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>Campus</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -485,6 +490,11 @@
           <t>Philippine Political Science Association</t>
         </is>
       </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>Main Campus</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -512,6 +522,11 @@
       <c r="G3" t="inlineStr">
         <is>
           <t>Sage Publications</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>Main Campus</t>
         </is>
       </c>
     </row>
